--- a/resources/reselling/files/reselling-int-category-pick.xlsx
+++ b/resources/reselling/files/reselling-int-category-pick.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,11 +62,6 @@
       <color rgb="000C2733"/>
       <sz val="11"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -156,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,8 +185,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -557,10 +550,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="76" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -615,7 +608,7 @@
     <row r="6" ht="33" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Margin — clears your floor after fees, postage, packing, allowance, time?</t>
+          <t>Margin — clears your floor after fees, shipping, packing, allowance, time?</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -828,10 +821,6 @@
           <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
         </is>
       </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/resources/reselling/files/reselling-int-category-pick.xlsx
+++ b/resources/reselling/files/reselling-int-category-pick.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,10 @@
       <color rgb="000C2733"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -151,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,6 +189,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -818,9 +823,13 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — Free resources: eports.global/resources/reselling</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
